--- a/output/pdf_financials_xlsx/ALT.xlsx
+++ b/output/pdf_financials_xlsx/ALT.xlsx
@@ -1315,10 +1315,10 @@
         <v>-7.11772</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.703627</v>
+        <v>-1.078327</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2.075312</v>
+        <v>-2.075312</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-0.711301</v>
@@ -1327,25 +1327,25 @@
         <v>4.224575</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.543345</v>
+        <v>-1.543345</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.68613</v>
+        <v>-0.68613</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.250744</v>
+        <v>-0.250744</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.264424</v>
+        <v>-0.264424</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.620368</v>
+        <v>-0.620368</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.710863</v>
+        <v>-0.710863</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.608864</v>
+        <v>-0.608864</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>-0.912367</v>
@@ -1385,7 +1385,7 @@
         <v>1.503141</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-8.449149999999999</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -1631,37 +1631,37 @@
         <v>-7.11772</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.890977</v>
+        <v>-0.890977</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.075312</v>
+        <v>-2.075312</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>0.79184</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>4.224575</v>
+        <v>-4.224575</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.543345</v>
+        <v>-1.543345</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.68613</v>
+        <v>-0.68613</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.250744</v>
+        <v>-0.250744</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.264424</v>
+        <v>-0.264424</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.620368</v>
+        <v>-0.620368</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.710863</v>
+        <v>-0.710863</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.608864</v>
+        <v>-0.608864</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>-0.912367</v>
@@ -1814,37 +1814,37 @@
         <v>-7.11772</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.890977</v>
+        <v>-0.890977</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2.075312</v>
+        <v>-2.075312</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>0.79184</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>4.224575</v>
+        <v>-4.224575</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.543345</v>
+        <v>-1.543345</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.68613</v>
+        <v>-0.68613</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.250744</v>
+        <v>-0.250744</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.264424</v>
+        <v>-0.264424</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.620368</v>
+        <v>-0.620368</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.710863</v>
+        <v>-0.710863</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.608864</v>
+        <v>-0.608864</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>-0.912367</v>
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>140.819167</v>
+        <v>-140.819167</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
         <v>-7.11772</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.703627</v>
+        <v>-1.078327</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.075312</v>
+        <v>-2.075312</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.711301</v>
@@ -2120,25 +2120,25 @@
         <v>4.224575</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.543345</v>
+        <v>-1.543345</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.68613</v>
+        <v>-0.68613</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.250744</v>
+        <v>-0.250744</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.264424</v>
+        <v>-0.264424</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.620368</v>
+        <v>-0.620368</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.710863</v>
+        <v>-0.710863</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.608864</v>
+        <v>-0.608864</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-0.912367</v>
@@ -2230,10 +2230,10 @@
         <v>-7.11772</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.703627</v>
+        <v>-1.078327</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.075312</v>
+        <v>-2.075312</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.711301</v>
@@ -2242,25 +2242,25 @@
         <v>4.224575</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.543345</v>
+        <v>-1.543345</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.68613</v>
+        <v>-0.68613</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.250744</v>
+        <v>-0.250744</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.264424</v>
+        <v>-0.264424</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.620368</v>
+        <v>-0.620368</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.710863</v>
+        <v>-0.710863</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.608864</v>
+        <v>-0.608864</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-0.912367</v>
@@ -2388,37 +2388,37 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>26.62632332187366</v>
+        <v>-17.37413604593041</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-211.3227733406814</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>-0</v>
@@ -46831,10 +46831,10 @@
         </is>
       </c>
       <c r="L363" s="5" t="n">
-        <v>0.563469</v>
+        <v>-0.563469</v>
       </c>
       <c r="M363" s="5" t="n">
-        <v>0.250744</v>
+        <v>-0.250744</v>
       </c>
       <c r="N363" t="inlineStr">
         <is>
@@ -46847,10 +46847,10 @@
         </is>
       </c>
       <c r="P363" s="5" t="n">
-        <v>0.710863</v>
+        <v>-0.710863</v>
       </c>
       <c r="Q363" s="5" t="n">
-        <v>0.608864</v>
+        <v>-0.608864</v>
       </c>
       <c r="R363" t="inlineStr">
         <is>
@@ -47454,10 +47454,10 @@
         </is>
       </c>
       <c r="K369" s="5" t="n">
-        <v>1.543345</v>
+        <v>-1.543345</v>
       </c>
       <c r="L369" s="5" t="n">
-        <v>0.563469</v>
+        <v>-0.563469</v>
       </c>
       <c r="M369" t="inlineStr">
         <is>
@@ -47470,10 +47470,10 @@
         </is>
       </c>
       <c r="O369" s="5" t="n">
-        <v>0.620368</v>
+        <v>-0.620368</v>
       </c>
       <c r="P369" s="5" t="n">
-        <v>0.710863</v>
+        <v>-0.710863</v>
       </c>
       <c r="Q369" t="inlineStr">
         <is>
@@ -48739,10 +48739,10 @@
         </is>
       </c>
       <c r="N381" s="5" t="n">
-        <v>0.264424</v>
+        <v>-0.264424</v>
       </c>
       <c r="O381" s="5" t="n">
-        <v>0.620368</v>
+        <v>-0.620368</v>
       </c>
       <c r="P381" t="inlineStr">
         <is>
@@ -50116,10 +50116,10 @@
         </is>
       </c>
       <c r="M394" s="5" t="n">
-        <v>0.250744</v>
+        <v>-0.250744</v>
       </c>
       <c r="N394" s="5" t="n">
-        <v>0.264424</v>
+        <v>-0.264424</v>
       </c>
       <c r="O394" t="inlineStr">
         <is>
@@ -51173,10 +51173,10 @@
         </is>
       </c>
       <c r="L404" s="5" t="n">
-        <v>0.68613</v>
+        <v>-0.68613</v>
       </c>
       <c r="M404" s="5" t="n">
-        <v>0.550744</v>
+        <v>-0.550744</v>
       </c>
       <c r="N404" t="inlineStr">
         <is>
@@ -53271,10 +53271,10 @@
         </is>
       </c>
       <c r="J424" s="5" t="n">
-        <v>4.224575</v>
+        <v>-4.224575</v>
       </c>
       <c r="K424" s="5" t="n">
-        <v>1.543345</v>
+        <v>-1.543345</v>
       </c>
       <c r="L424" t="inlineStr">
         <is>
@@ -53591,10 +53591,10 @@
         </is>
       </c>
       <c r="J427" s="5" t="n">
-        <v>4.213191</v>
+        <v>-4.213191</v>
       </c>
       <c r="K427" s="5" t="n">
-        <v>1.543345</v>
+        <v>-1.543345</v>
       </c>
       <c r="L427" t="inlineStr">
         <is>
@@ -55990,10 +55990,10 @@
         <v>-7.11772</v>
       </c>
       <c r="G450" s="5" t="n">
-        <v>0.890977</v>
+        <v>-0.890977</v>
       </c>
       <c r="H450" s="5" t="n">
-        <v>2.075312</v>
+        <v>-2.075312</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ALT.xlsx
+++ b/output/pdf_financials_xlsx/ALT.xlsx
@@ -2585,22 +2585,22 @@
         <v>0.037364</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.021564</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.06812799999999999</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.018901</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.064348</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.006994</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.036171</v>
       </c>
     </row>
     <row r="35">
@@ -2711,22 +2711,22 @@
         <v>0.037364</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.021564</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>1.003161</v>
+        <v>1.071289</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.323893</v>
+        <v>0.342794</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.075865</v>
+        <v>0.140213</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.191118</v>
+        <v>0.198112</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.06657299999999999</v>
+        <v>0.102744</v>
       </c>
     </row>
     <row r="37">
@@ -3467,22 +3467,22 @@
         <v>0.002171</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.022417</v>
+        <v>0.000853</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.078597</v>
+        <v>0.010469</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.036926</v>
+        <v>0.018025</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.06605</v>
+        <v>0.001702</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.202539</v>
+        <v>0.195545</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.0751</v>
+        <v>0.038929</v>
       </c>
     </row>
     <row r="49">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/ALT.xlsx
+++ b/output/pdf_financials_xlsx/ALT.xlsx
@@ -2172,31 +2172,31 @@
         <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.008985999999999999</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.01187</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.016139</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.016293</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.007732</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.007218</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.004909</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.001705</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.003417</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>0</v>
@@ -2233,31 +2233,31 @@
         <v>-1.078327</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.075312</v>
+        <v>-2.066326</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.711301</v>
+        <v>-0.699431</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>4.224575</v>
+        <v>4.240714</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.543345</v>
+        <v>-1.527052</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.68613</v>
+        <v>-0.6783979999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.250744</v>
+        <v>-0.243526</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.264424</v>
+        <v>-0.259515</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.620368</v>
+        <v>-0.618663</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.710863</v>
+        <v>-0.707446</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-0.608864</v>
@@ -6726,31 +6726,31 @@
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.008985999999999999</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.01187</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.016139</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.016293</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.007732</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.007218</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.004909</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.001705</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.003417</v>
       </c>
       <c r="N100" s="3" t="n">
         <v>0</v>
@@ -29008,7 +29008,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -30916,7 +30920,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -51550,7 +51558,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ALT.xlsx
+++ b/output/pdf_financials_xlsx/ALT.xlsx
@@ -2750,10 +2750,10 @@
         <v>0.058364</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0</v>
+        <v>0.130261</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>0.01669</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>0.007003</v>
@@ -3002,10 +3002,10 @@
         <v>0.058364</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>0.130261</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>0.01669</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>0.007003</v>
@@ -3443,10 +3443,10 @@
         <v>0.00308</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.014466</v>
+        <v>0.884205</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.043579</v>
+        <v>0.026889</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.022504</v>
@@ -3972,13 +3972,13 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>0.103392</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>0.103392</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>0.112377</v>
       </c>
       <c r="F56" s="3" t="n">
         <v>0</v>
@@ -4035,13 +4035,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>0.040369</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>0.057546</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>0.06653100000000001</v>
       </c>
       <c r="F57" s="3" t="n">
         <v>0</v>
@@ -7494,7 +7494,7 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -33238,7 +33238,11 @@
           <t>Proceeds on disposition of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -33448,7 +33452,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
